--- a/jpcore-r4b/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -675,7 +675,7 @@
 このプロファイルではHL70421 Severity of Illness Code（MI 軽度, MO 中度, SE 重度）を採用。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConditionSeverity_VS|2.0.0-dev</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -1107,7 +1107,7 @@
     <t>JP_ConditionDiseaseCodeICD10_VSの中から適切なコードを指定する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/ICD10-2013-full|2.0.0-dev-temp</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/ValueSet/ICD10-2013-full|2.0.0-dev</t>
   </si>
   <si>
     <t>Condition.code.coding:icd10.id</t>
@@ -1899,7 +1899,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.63671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4b/develop/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="494">
   <si>
     <t>Property</t>
   </si>
@@ -278,8 +278,8 @@
 健康上の懸念となるレベルに達した、身体的、精神的、社会的な負の状態(condition)や問題（problem／issue）、医療者による診断(diagnosis)、生じたイベント(event)、置かれている状況(situation)、臨床的概念(clinical concept)。</t>
   </si>
   <si>
-    <t>con-3:Condition.clinicalStatus SHOULD be present if verificationStatus is not entered-in-error and category is problem-list-item {verificationStatus.empty().not() and verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').exists().not() and category.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-category' and code='problem-list-item').exists() implies clinicalStatus.empty().not()}
-con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>con-3:verificationStatus」が「entered-in-error」でなく、「category」が「problem-list-item」である場合、「condition.clinicalStatus」が存在している必要があります。 / Condition.clinicalStatus SHOULD be present if verificationStatus is not entered-in-error and category is problem-list-item {verificationStatus.empty().not() and verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').exists().not() and category.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-category' and code='problem-list-item').exists() implies clinicalStatus.empty().not()}
+con-4:もし状態が軽減された場合、臨床状態は不活動、解決、または寛解でなければなりません。 / If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:verificationStatusがentered-in-errorである場合、condition.clinicalStatusは存在してはなりません。 / Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -310,13 +310,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -349,13 +349,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -368,19 +368,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>人間の言語。 / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -403,10 +403,10 @@
     <t>Text summary of the resource, for human interpretation. このリソースを人間が解釈するためのテキスト要約</t>
   </si>
   <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -426,19 +426,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>含まれている、インラインのリソース / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -468,8 +468,8 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.extension:diseaseOutcome</t>
@@ -493,8 +493,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.modifierExtension</t>
@@ -504,17 +504,17 @@
 user content</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>修飾子拡張により、安全に無視できない拡張を、安全に無視できる大多数の拡張と明確に区別することができます。これにより、実装者が拡張の存在を禁止する必要がなくなり、相互運用性が促進されます。詳細については、[修飾子拡張の定義](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension)を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -527,16 +527,16 @@
 </t>
   </si>
   <si>
-    <t>External Ids for this condition</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
+    <t>この状態の外部ID。 / External Ids for this condition</t>
+  </si>
+  <si>
+    <t>サーバーからサーバーへ伝搬するにつれて更新され、パフォーマーまたは他のシステムによって割り当てられたビジネスidentifierが、この状態に対して一定の値を保持します。 / Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[discussion]（resource.html＃identifiers）を参照）。 identifierが単一のリソースインスタンスにのみ表示されることが最善の方法ですが、ビジネス上の実践によっては、同じidentifierを持つ複数のリソースインスタンスが存在する場合があります。 たとえば、複数の患者と個人リソースインスタンスが同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>様々な参加システムによって知られている状態の識別を可能にし、サーバー間で一貫性を保つ方法で識別できるようにする。 / Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -568,7 +568,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>The clinical status of the condition or diagnosis.</t>
+    <t>病態や診断の臨床状態。 / The clinical status of the condition or diagnosis.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-clinical|4.3.0</t>
@@ -607,7 +607,7 @@
     <t>疑い病名を指定するのに使用する。疑い病名の場合は 'unconfirmed'を、確定病名の場合は'confirmed'をそれぞれ指定する。</t>
   </si>
   <si>
-    <t>The verification status to support or decline the clinical status of the condition or diagnosis.</t>
+    <t>状態や診断の臨床状況を支持または拒否するための検証状況 / The verification status to support or decline the clinical status of the condition or diagnosis.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-ver-status|4.3.0</t>
@@ -636,10 +636,10 @@
     <t>problem-list-item | encounter-diagnosis（プロブレムリスト | 一時的な診断）</t>
   </si>
   <si>
-    <t>A category assigned to the condition.</t>
-  </si>
-  <si>
-    <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
+    <t>状態に割り当てられたカテゴリー。 / A category assigned to the condition.</t>
+  </si>
+  <si>
+    <t>分類はしばしば文脈に強く依存しており、他の文脈では区別が不十分であるか、あまり役に立たないように見えることがあります。 / The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -709,13 +709,13 @@
     <t>JP_Condition_DiseaseCode_VSの中から適切な病名識別コードを指定する</t>
   </si>
   <si>
-    <t>0..1 to account for primarily narrative only resources.</t>
+    <t>主にナラティブのみのリソースを考慮して0..1としている。 / 0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Identification of the condition or diagnosis.</t>
+    <t>状態や診断の特定 / Identification of the condition or diagnosis.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
@@ -751,10 +751,10 @@
     <t>Condition.code.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -766,16 +766,23 @@
     <t>Condition.code.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Condition.code.extension:diseasePrefixModifier</t>
@@ -819,16 +826,16 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -838,6 +845,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
@@ -880,16 +891,16 @@
     <t>Condition.code.coding.system</t>
   </si>
   <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
     <t>http://medis.or.jp/CodeSystem/master-disease-exCode</t>
@@ -914,13 +925,13 @@
 </t>
   </si>
   <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
   </si>
   <si>
     <t>Coding.version</t>
@@ -938,13 +949,13 @@
     <t>Condition.code.coding.code</t>
   </si>
   <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -962,13 +973,13 @@
     <t>Condition.code.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -990,16 +1001,16 @@
 </t>
   </si>
   <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
   </si>
   <si>
     <t>Coding.userSelected</t>
@@ -1146,7 +1157,7 @@
     <t>修飾語などを含めた病名や所見、症状のフルテキストを記述する。特に所見や症状などでコード化が難しい場合は、ここにテキストとして記述する。</t>
   </si>
   <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -1164,13 +1175,13 @@
     <t>Anatomical location, if relevant. もし関連するのであれば、その人体部位</t>
   </si>
   <si>
-    <t>The anatomical location where this condition manifests itself.</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
-  </si>
-  <si>
-    <t>SNOMED CT Body site concepts</t>
+    <t>この症状が現れる解剖学的位置。 / The anatomical location where this condition manifests itself.</t>
+  </si>
+  <si>
+    <t>Condition.code」で暗黙的に表現されない場合にのみ使用します。ユースケースがBodySiteリソースから属性を必要とする場合（例えば、別々に識別して追跡するために）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用してください。概要コードであることも、位置の非常に正確な定義への参照であることもあります。 / Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
+  </si>
+  <si>
+    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。 / SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
@@ -1199,10 +1210,10 @@
     <t>Who has the condition? 誰がこの状態を有するか</t>
   </si>
   <si>
-    <t>Indicates the patient or group who the condition record is associated with.</t>
-  </si>
-  <si>
-    <t>Group is typically used for veterinary or public health use cases.</t>
+    <t>その病状記録が関連する患者またはグループを示します。 / Indicates the patient or group who the condition record is associated with.</t>
+  </si>
+  <si>
+    <t>Groupは通常、獣医学または公衆衛生のユースケースに使用される。 / Group is typically used for veterinary or public health use cases.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1231,7 +1242,7 @@
 この患者状態の記録やレコード作成に関連する受療の状況（外来、入院、救急、在宅など）</t>
   </si>
   <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
+    <t>通常、イベントが発生した受療行動の中で行われることが多いですが、公式的に受療行動が完了する前または後に開始される場合がありますが、それでも受療行動の文脈に関連する活動があります。この記録は、この特定の記録が関連付けられた出来事を示します。 「新しい」診断が、継続的に修正された情報を反映する場合、これは最初に患者が変化に気づいた最初の受療行動とは異なる場合があります。 / This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter. This record indicates the encounter this particular record is associated with.  In the case of a "new" diagnosis reflecting ongoing/revised information about the condition, this might be distinct from the first encounter in which the underlying condition was first "known".</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1376,8 +1387,8 @@
 病状の臨床病期またはグレード。正式な重症度評価を含む場合がある。</t>
   </si>
   <si>
-    <t>con-1:Stage SHALL have summary or assessment {summary.exists() or assessment.exists()}
-ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
+    <t>con-1:ステージには要約または評価が必要です。 / Stage SHALL have summary or assessment {summary.exists() or assessment.exists()}
+ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage/grade"]</t>
@@ -1386,7 +1397,19 @@
     <t>Condition.stage.id</t>
   </si>
   <si>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>Condition.stage.extension</t>
+  </si>
+  <si>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Condition.stage.modifierExtension</t>
@@ -1396,10 +1419,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1409,13 +1433,13 @@
     <t>Condition.stage.summary</t>
   </si>
   <si>
-    <t>Simple summary (disease specific)</t>
-  </si>
-  <si>
-    <t>A simple summary of the stage such as "Stage 3". The determination of the stage is disease-specific.</t>
-  </si>
-  <si>
-    <t>Codes describing condition stages (e.g. Cancer stages).</t>
+    <t>簡単な要約（病気特有のもの） / Simple summary (disease specific)</t>
+  </si>
+  <si>
+    <t>ステージ3」といった、単純なステージの概要。ステージの決定は病気によって異なります。 / A simple summary of the stage such as "Stage 3". The determination of the stage is disease-specific.</t>
+  </si>
+  <si>
+    <t>状態段階を説明するコード（例：がんの段階） / Codes describing condition stages (e.g. Cancer stages).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-stage|4.3.0</t>
@@ -1435,10 +1459,10 @@
 </t>
   </si>
   <si>
-    <t>Formal record of assessment</t>
-  </si>
-  <si>
-    <t>Reference to a formal record of the evidence on which the staging assessment is based.</t>
+    <t>評価の公式記録 / Formal record of assessment</t>
+  </si>
+  <si>
+    <t>ステージング評価の根拠となる正式な証拠記録への参照。 / Reference to a formal record of the evidence on which the staging assessment is based.</t>
   </si>
   <si>
     <t>.self</t>
@@ -1447,13 +1471,13 @@
     <t>Condition.stage.type</t>
   </si>
   <si>
-    <t>Kind of staging</t>
-  </si>
-  <si>
-    <t>The kind of staging, such as pathological or clinical staging.</t>
-  </si>
-  <si>
-    <t>Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
+    <t>ステージングの種類 / Kind of staging</t>
+  </si>
+  <si>
+    <t>病理的ステージングや臨床ステージングといった種類のステージング / The kind of staging, such as pathological or clinical staging.</t>
+  </si>
+  <si>
+    <t>状態分類を表すコード（例：臨床的または病理学的）。 / Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.3.0</t>
@@ -1472,11 +1496,11 @@
 患者状態を確認または否定した証拠など、状態の検証ステータスの裏付けとなる症状や兆候。</t>
   </si>
   <si>
-    <t>The evidence may be a simple list of coded symptoms/manifestations, or references to observations or formal assessments, or both.</t>
-  </si>
-  <si>
-    <t>con-2:evidence SHALL have code or details {code.exists() or detail.exists()}
-ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
+    <t>証拠は、コード化された症状/症状の簡単なリスト、または観察や正式な評価への言及、またはその両方である可能性があります。 / The evidence may be a simple list of coded symptoms/manifestations, or references to observations or formal assessments, or both.</t>
+  </si>
+  <si>
+    <t>con-2:証拠にはコードまたは詳細が必要です。 / evidence SHALL have code or details {code.exists() or detail.exists()}
+ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=SPRT].target[classCode=OBS, moodCode=EVN]</t>
@@ -1500,7 +1524,7 @@
     <t>この状態の記録に至った徴候や症状。</t>
   </si>
   <si>
-    <t>Codes that describe the manifestation or symptoms of a condition.</t>
+    <t>症状や現れ方を記述するコード。 / Codes that describe the manifestation or symptoms of a condition.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.3.0</t>
@@ -1526,10 +1550,10 @@
 </t>
   </si>
   <si>
-    <t>Supporting information found elsewhere</t>
-  </si>
-  <si>
-    <t>Links to other relevant information, including pathology reports.</t>
+    <t>別の場所で見つかったサポート情報 / Supporting information found elsewhere</t>
+  </si>
+  <si>
+    <t>その他関連情報、病理検査報告書などのリンク。 / Links to other relevant information, including pathology reports.</t>
   </si>
   <si>
     <t>Condition.note</t>
@@ -1898,7 +1922,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="73.078125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="100.0703125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="53.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -4116,7 +4140,7 @@
         <v>236</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4157,7 +4181,7 @@
         <v>142</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>80</v>
@@ -4166,7 +4190,7 @@
         <v>143</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4178,7 +4202,7 @@
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
@@ -4201,13 +4225,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>234</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>80</v>
@@ -4229,13 +4253,13 @@
         <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4286,7 +4310,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4298,7 +4322,7 @@
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>80</v>
@@ -4321,13 +4345,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>234</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>80</v>
@@ -4349,13 +4373,13 @@
         <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4406,7 +4430,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4418,7 +4442,7 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
@@ -4441,10 +4465,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4467,19 +4491,19 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4516,7 +4540,7 @@
         <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4526,7 +4550,7 @@
         <v>143</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4538,7 +4562,7 @@
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>80</v>
@@ -4547,10 +4571,10 @@
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -4561,13 +4585,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>80</v>
@@ -4589,19 +4613,19 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4630,7 +4654,7 @@
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4648,7 +4672,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4660,7 +4684,7 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
@@ -4669,10 +4693,10 @@
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -4683,10 +4707,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4801,10 +4825,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4836,7 +4860,7 @@
         <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4877,7 +4901,7 @@
         <v>142</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>80</v>
@@ -4886,7 +4910,7 @@
         <v>143</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4898,7 +4922,7 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
@@ -4921,10 +4945,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4950,23 +4974,23 @@
         <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>80</v>
@@ -5008,7 +5032,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5020,7 +5044,7 @@
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
@@ -5029,10 +5053,10 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>80</v>
@@ -5043,10 +5067,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5069,16 +5093,16 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5128,7 +5152,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5140,7 +5164,7 @@
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -5149,10 +5173,10 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
@@ -5163,10 +5187,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5192,14 +5216,14 @@
         <v>113</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5248,7 +5272,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5260,7 +5284,7 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5269,10 +5293,10 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
@@ -5283,10 +5307,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5309,17 +5333,17 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5368,7 +5392,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5380,7 +5404,7 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5389,10 +5413,10 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
@@ -5403,10 +5427,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5429,19 +5453,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
@@ -5490,7 +5514,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5502,7 +5526,7 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -5511,10 +5535,10 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>80</v>
@@ -5525,13 +5549,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>80</v>
@@ -5553,19 +5577,19 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5594,7 +5618,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5612,7 +5636,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5624,7 +5648,7 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
@@ -5633,10 +5657,10 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -5647,10 +5671,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5765,10 +5789,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5800,7 +5824,7 @@
         <v>236</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5841,7 +5865,7 @@
         <v>142</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>80</v>
@@ -5850,7 +5874,7 @@
         <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5862,7 +5886,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5885,10 +5909,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5914,23 +5938,23 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>80</v>
@@ -5972,7 +5996,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5984,7 +6008,7 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -5993,10 +6017,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6007,10 +6031,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6033,16 +6057,16 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6092,7 +6116,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6104,7 +6128,7 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
@@ -6113,10 +6137,10 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6127,10 +6151,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6156,14 +6180,14 @@
         <v>113</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6212,7 +6236,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6224,7 +6248,7 @@
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6233,10 +6257,10 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6247,10 +6271,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6273,17 +6297,17 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6332,7 +6356,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6344,7 +6368,7 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -6353,10 +6377,10 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6367,10 +6391,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6393,19 +6417,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6454,7 +6478,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6466,7 +6490,7 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -6475,10 +6499,10 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -6489,13 +6513,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
@@ -6517,19 +6541,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6558,7 +6582,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6576,7 +6600,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6588,7 +6612,7 @@
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6597,10 +6621,10 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -6611,10 +6635,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6729,10 +6753,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6764,7 +6788,7 @@
         <v>236</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6805,7 +6829,7 @@
         <v>142</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>80</v>
@@ -6814,7 +6838,7 @@
         <v>143</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6826,7 +6850,7 @@
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6849,10 +6873,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6878,23 +6902,23 @@
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>80</v>
@@ -6936,7 +6960,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6948,7 +6972,7 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -6957,10 +6981,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -6971,10 +6995,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6997,16 +7021,16 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7056,7 +7080,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7068,7 +7092,7 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
@@ -7077,10 +7101,10 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7091,10 +7115,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7120,14 +7144,14 @@
         <v>113</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7176,7 +7200,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7188,7 +7212,7 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -7197,10 +7221,10 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -7211,10 +7235,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7237,17 +7261,17 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7296,7 +7320,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7308,7 +7332,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7317,10 +7341,10 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -7331,10 +7355,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7357,19 +7381,19 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7418,7 +7442,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7430,7 +7454,7 @@
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7439,10 +7463,10 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7453,13 +7477,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>80</v>
@@ -7481,19 +7505,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7522,7 +7546,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7540,7 +7564,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7552,7 +7576,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7561,10 +7585,10 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7575,10 +7599,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7693,10 +7717,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7728,7 +7752,7 @@
         <v>236</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>157</v>
+        <v>237</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7769,7 +7793,7 @@
         <v>142</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>80</v>
@@ -7778,7 +7802,7 @@
         <v>143</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7790,7 +7814,7 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>145</v>
+        <v>240</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
@@ -7813,10 +7837,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7842,23 +7866,23 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>80</v>
@@ -7900,7 +7924,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7912,7 +7936,7 @@
         <v>80</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -7921,10 +7945,10 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -7935,10 +7959,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7961,16 +7985,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8020,7 +8044,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8032,7 +8056,7 @@
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -8041,10 +8065,10 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -8055,10 +8079,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8084,14 +8108,14 @@
         <v>113</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8140,7 +8164,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8152,7 +8176,7 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
@@ -8161,10 +8185,10 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8175,10 +8199,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8201,17 +8225,17 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8260,7 +8284,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8272,7 +8296,7 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
@@ -8281,10 +8305,10 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8295,10 +8319,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8321,19 +8345,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8382,7 +8406,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8394,7 +8418,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8403,10 +8427,10 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8417,10 +8441,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8443,19 +8467,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8504,7 +8528,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8516,7 +8540,7 @@
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
@@ -8525,10 +8549,10 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -8539,10 +8563,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8568,13 +8592,13 @@
         <v>170</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8603,10 +8627,10 @@
         <v>220</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8624,7 +8648,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8642,31 +8666,31 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8685,17 +8709,17 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8744,7 +8768,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>93</v>
@@ -8759,19 +8783,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -8779,10 +8803,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8805,16 +8829,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8864,7 +8888,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8879,19 +8903,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -8899,10 +8923,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8925,16 +8949,16 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8984,7 +9008,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8999,19 +9023,19 @@
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9019,10 +9043,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9045,16 +9069,16 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9104,7 +9128,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9113,7 +9137,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9128,10 +9152,10 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9139,10 +9163,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9165,13 +9189,13 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9222,7 +9246,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9243,13 +9267,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9257,10 +9281,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9283,13 +9307,13 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9340,7 +9364,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9364,10 +9388,10 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9375,10 +9399,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9401,13 +9425,13 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9458,7 +9482,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9479,13 +9503,13 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>80</v>
@@ -9493,10 +9517,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9519,13 +9543,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9576,7 +9600,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9588,7 +9612,7 @@
         <v>80</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>80</v>
@@ -9600,7 +9624,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9611,10 +9635,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9637,13 +9661,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>230</v>
+        <v>437</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>231</v>
+        <v>438</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9729,10 +9753,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9758,10 +9782,10 @@
         <v>139</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>235</v>
+        <v>440</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>236</v>
+        <v>441</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>157</v>
@@ -9814,7 +9838,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9849,14 +9873,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9878,10 +9902,10 @@
         <v>139</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>157</v>
@@ -9936,7 +9960,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9971,10 +9995,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10000,10 +10024,10 @@
         <v>170</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10033,10 +10057,10 @@
         <v>220</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10054,7 +10078,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10063,7 +10087,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10072,7 +10096,7 @@
         <v>80</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>180</v>
@@ -10089,10 +10113,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10115,13 +10139,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10172,7 +10196,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10181,7 +10205,7 @@
         <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10196,7 +10220,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -10207,10 +10231,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10236,10 +10260,10 @@
         <v>170</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10269,10 +10293,10 @@
         <v>220</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -10290,7 +10314,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10314,7 +10338,7 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10325,10 +10349,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10351,16 +10375,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10410,7 +10434,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10422,7 +10446,7 @@
         <v>80</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -10434,7 +10458,7 @@
         <v>80</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -10445,10 +10469,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10471,13 +10495,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>230</v>
+        <v>437</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>231</v>
+        <v>438</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10563,10 +10587,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10592,10 +10616,10 @@
         <v>139</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>235</v>
+        <v>440</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>236</v>
+        <v>441</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>157</v>
@@ -10648,7 +10672,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10683,14 +10707,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10712,10 +10736,10 @@
         <v>139</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>157</v>
@@ -10770,7 +10794,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10805,10 +10829,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10834,10 +10858,10 @@
         <v>170</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10867,10 +10891,10 @@
         <v>220</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -10888,7 +10912,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10897,13 +10921,13 @@
         <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>200</v>
@@ -10912,10 +10936,10 @@
         <v>80</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>80</v>
@@ -10923,10 +10947,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10949,13 +10973,13 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11006,7 +11030,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11015,7 +11039,7 @@
         <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>105</v>
@@ -11030,10 +11054,10 @@
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>80</v>
@@ -11041,10 +11065,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11067,13 +11091,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11124,7 +11148,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11139,16 +11163,16 @@
         <v>105</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
